--- a/EstablecimientoSalud/excels/TUMBES-TUMBES-TUMBES.xlsx
+++ b/EstablecimientoSalud/excels/TUMBES-TUMBES-TUMBES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,27 +518,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.5473191</t>
+          <t>-3.5695573</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-80.4004827</t>
+          <t>-80.4606256</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>UNIDAD CLINICA</t>
+          <t>POLICLINICO MILITAR "GRAL BRIG JORGE GUIMAC BONIFAZ"</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AVENIDA AV. PANAMERICANA NORTE KM 1275. PUERTO EL CURA. TUMBES DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>AVENIDA AV. TACNA Nº 101 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.55665808</t>
+          <t>-3.56101629</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-80.45026547</t>
+          <t>-80.42115009</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO  FAMILIA</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "VIRGEN DEL CISNE"</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CALLE AGRICULTURA PISO 1 MANZANA O LOTE B DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>OTROS VIRGEN DEL CISNE ASENTAMIENTO HUMANO L 03 FRENTE A COMPLEJO DEPORTIVO "VIRGEN DEL CISNE" TUMBES TUMBES TUMBES</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.55545937</t>
+          <t>-3.56954711</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-80.4301042</t>
+          <t>-80.44642904</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO TRAUMATOLOGICO DEL NORTE</t>
+          <t>CENTRO DE SALUD MILITAR VIRGEN DE FATIMA DE LA 9Âª BRIGADA BLINDADA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CALLE CARLOS VASQUEZ MANZANA 4 LOTE 2 URBANIZACION ANDRES ARAUJO DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>PROLONGACION HILARIO CARRASCO SIN NUMERO - TABLAZO DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,27 +704,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.5564921</t>
+          <t>-3.5037058</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-80.4270885</t>
+          <t>-80.3909164</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>POLICLINICO SAN FRANCISCO</t>
+          <t>CENTRO DE SALUD - E.P. TUMBES-ORN-INPE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JR. JAEN Nº 211 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>OTROS PANAMERICANA NORTE CRUCE CON PUERTO PIZARRO DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.5695573</t>
+          <t>-3.58217906</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-80.4606256</t>
+          <t>-80.42026826</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>POLICLINICO MILITAR "GRAL BRIG JORGE GUIMAC BONIFAZ"</t>
+          <t>PAMPA GRANDE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AVENIDA AV. TACNA Nº 101 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>AVENIDA AV. SIMON BOLIVAR NÂ° 304 PAMPA GRANDE AV. SIMON BOLIVAR NÂ° 304 PAMPA GRANDE TUMBES TUMBES TUMBES</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>23014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.56863777</t>
+          <t>-3.56242441</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-80.45701122</t>
+          <t>-80.45615292</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLOGICO PALACIOS</t>
+          <t>GERARDO GONZALES VILLEGAS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CALLE HUASCAR NUMERO 540 PISO 2 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>CALLE CALLE 24 julio NUMERO 565 CALLE 24 julio NUMERO 565 TUMBES TUMBES TUMBES</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7865</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.5719136</t>
+          <t>-3.55700516</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-80.4591247</t>
+          <t>-80.42750694</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLAGICO AMERICANO - TUMBES</t>
+          <t>CLAS ANDRES ARAUJO MORAN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CALLE CALLE LOS ANDES Nº 121 TUMBES DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
+          <t>OTROS URB.LISNHERT TUDELA MZ X LT 01 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.56101629</t>
+          <t>-3.503105</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-80.42115009</t>
+          <t>-80.39182833</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "VIRGEN DEL CISNE"</t>
+          <t>PUERTO PIZARRO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OTROS VIRGEN DEL CISNE ASENTAMIENTO HUMANO L 03 FRENTE A COMPLEJO DEPORTIVO "VIRGEN DEL CISNE" TUMBES TUMBES TUMBES</t>
+          <t>AVENIDA AV. JOSE OLAYA S/N PTO. PIZARRO S/N AV. JOSE OLAYA S/N PTO. PIZARRO TUMBES TUMBES TUMBES</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.57448701</t>
+          <t>-3.5599234</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-80.45598126</t>
+          <t>-80.4546507</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO OBSTETRICO GENESIS</t>
+          <t>ENFERMERIA VILLA NAVAL -TUMBES</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CALLE MAYNAS 411 1 COSTADO CUARTEL PONTONEROS TUMBES TUMBES TUMBES</t>
+          <t>AVENIDA AV. LOS TUMPIS S/N VILLA NAVAL -TUMBES S/N AV. LOS TUMPIS S/N VILLA NAVAL -TUMBES TUMBES TUMBES TUMBES</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1043,378 +1043,6 @@
         </is>
       </c>
       <c r="L10" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>11996</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-3.56954711</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-80.44642904</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>CENTRO DE SALUD MILITAR VIRGEN DE FATIMA DE LA 9Âª BRIGADA BLINDADA</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PROLONGACION HILARIO CARRASCO SIN NUMERO - TABLAZO DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>18438</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-3.5037058</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-80.3909164</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>CENTRO DE SALUD - E.P. TUMBES-ORN-INPE</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>OTROS PANAMERICANA NORTE CRUCE CON PUERTO PIZARRO DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>26467</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-3.5564921</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-80.4270885</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>CONSULTORIO MEDICO "SEAOR DE LUREN"</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CALLE ELIAS AGUIRRE MANZANA 02 LOTE 21 URBANIZACION ANDRES ARAUJO MORAN DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>23255</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-3.57238825</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-80.45518732</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO  VITALUZ</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>JAEN NUMERO 211 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>28487</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-3.56325161</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-80.45307911</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>CENTRO ODONTOLOGICO CHAVEZ</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CALLE Jose Olaya NUMERO 114 PISO 1 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>33335</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-3.5564921</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-80.4270885</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>POLICLINICO SALAZAR</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CALLE 24 DE JULIO NUMERO 512 DISTRITO TUMBES PROVINCIA TUMBES DEPARTAMENTO TUMBES</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>240101</t>
         </is>

--- a/EstablecimientoSalud/excels/TUMBES-TUMBES-TUMBES.xlsx
+++ b/EstablecimientoSalud/excels/TUMBES-TUMBES-TUMBES.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>20245</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-3.5695573</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>28923</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-3.56101629</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-3.56954711</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>18438</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-3.5037058</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>1882</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-3.58217906</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>23014</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-3.56242441</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-3.55700516</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>1883</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-3.503105</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>240101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>8017</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>240101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TUMBES</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-3.5599234</t>
@@ -1040,11 +995,6 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>240101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/TUMBES-TUMBES-TUMBES.xlsx
+++ b/EstablecimientoSalud/excels/TUMBES-TUMBES-TUMBES.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
